--- a/data-manipulation-scripts/sheets-cleanup/sheets/LAMPADA FREIO_.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/LAMPADA FREIO_.xlsx
@@ -31,13 +31,13 @@
     <t>7895099121612</t>
   </si>
   <si>
-    <t>LAMPADA FREIO IRON 12x21/5W 121520</t>
+    <t>LAMPADA FREIO TRASEIRO IRON 12x21/5W 121520</t>
   </si>
   <si>
     <t>7908193644441</t>
   </si>
   <si>
-    <t>LAMPADA FREIO GEAR 12V 21/ 5W</t>
+    <t>LAMPADA FREIO TRASEIRO GEAR 12V 21/ 5W</t>
   </si>
 </sst>
 </file>
@@ -95,10 +95,10 @@
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="bottom"/>
+      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+      <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
@@ -365,10 +365,12 @@
       <c r="B2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="5">
         <v>1.0</v>
       </c>
-      <c r="D2" s="5"/>
+      <c r="D2" s="4">
+        <v>6.0</v>
+      </c>
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
@@ -400,10 +402,12 @@
       <c r="B3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="5">
         <v>7.0</v>
       </c>
-      <c r="D3" s="5"/>
+      <c r="D3" s="4">
+        <v>6.0</v>
+      </c>
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
